--- a/Behind/Pimary VS Secondary.xlsx
+++ b/Behind/Pimary VS Secondary.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3479619E-CDC9-4E45-B631-6662658BDBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F18C05-8900-4AF2-A96B-1274F84AB131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B13BB3DE-45F3-4A08-8C5B-C8EF34D5413B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="July026" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -99,7 +99,10 @@
     <t>18/7/26</t>
   </si>
   <si>
-    <t>Till 28 july</t>
+    <t>30/7/26</t>
+  </si>
+  <si>
+    <t>Till 31 july</t>
   </si>
 </sst>
 </file>
@@ -675,23 +678,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4897FB-F3E4-4933-BDE3-BEDB17D2ED6F}">
-  <dimension ref="C5:N17"/>
+  <dimension ref="B5:O17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="44.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.54296875" customWidth="1"/>
-    <col min="12" max="12" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.54296875" customWidth="1"/>
+    <col min="13" max="13" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:14" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" ht="18.5" x14ac:dyDescent="0.35">
       <c r="D5" s="23" t="s">
         <v>21</v>
       </c>
@@ -705,8 +708,9 @@
       <c r="L5" s="23"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
-    </row>
-    <row r="6" spans="3:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="O5" s="23"/>
+    </row>
+    <row r="6" spans="2:15" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C6" s="9"/>
       <c r="D6" s="17" t="s">
         <v>0</v>
@@ -724,25 +728,35 @@
         <v>23</v>
       </c>
       <c r="I6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="K6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="L6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="17" t="s">
+      <c r="M6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="N6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="O6" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <f>C7*40</f>
+        <v>12000</v>
+      </c>
+      <c r="C7">
+        <v>300</v>
+      </c>
       <c r="D7" s="10" t="s">
         <v>3</v>
       </c>
@@ -757,29 +771,39 @@
         <f>300*40</f>
         <v>12000</v>
       </c>
-      <c r="I7" s="14">
-        <f t="shared" ref="I7:I13" si="0">F7+G7+H7</f>
-        <v>21586</v>
-      </c>
-      <c r="J7" s="5">
-        <v>13365</v>
-      </c>
-      <c r="K7" s="15">
-        <f>I7-J7</f>
-        <v>8221</v>
-      </c>
-      <c r="L7" s="16">
-        <v>8379</v>
-      </c>
-      <c r="M7" s="8">
-        <f>L7-K7</f>
-        <v>158</v>
-      </c>
-      <c r="N7" s="7">
+      <c r="I7" s="16">
+        <f>70*40</f>
+        <v>2800</v>
+      </c>
+      <c r="J7" s="14">
+        <f>F7+G7+H7+I7</f>
+        <v>24386</v>
+      </c>
+      <c r="K7" s="5">
+        <f>394.12*40</f>
+        <v>15764.8</v>
+      </c>
+      <c r="L7" s="15">
+        <f>J7-K7</f>
+        <v>8621.2000000000007</v>
+      </c>
+      <c r="M7" s="16"/>
+      <c r="N7" s="8">
+        <f>L7-M7</f>
+        <v>8621.2000000000007</v>
+      </c>
+      <c r="O7" s="7">
         <v>280</v>
       </c>
     </row>
-    <row r="8" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <f t="shared" ref="B8:B12" si="0">C8*40</f>
+        <v>8000</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
       <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
@@ -791,32 +815,38 @@
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13">
-        <f>200*40</f>
-        <v>8000</v>
-      </c>
-      <c r="I8" s="14">
+        <v>4000</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14">
+        <f t="shared" ref="J8:J13" si="1">F8+G8+H8+I8</f>
+        <v>14668</v>
+      </c>
+      <c r="K8" s="5">
+        <f>461.6*40</f>
+        <v>18464</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" ref="L8:L13" si="2">J8-K8</f>
+        <v>-3796</v>
+      </c>
+      <c r="M8" s="16"/>
+      <c r="N8" s="8">
+        <f t="shared" ref="N8:N13" si="3">L8-M8</f>
+        <v>-3796</v>
+      </c>
+      <c r="O8" s="7">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B9">
         <f t="shared" si="0"/>
-        <v>18668</v>
-      </c>
-      <c r="J8" s="5">
-        <v>13225</v>
-      </c>
-      <c r="K8" s="15">
-        <f t="shared" ref="K8:K13" si="1">I8-J8</f>
-        <v>5443</v>
-      </c>
-      <c r="L8" s="16">
-        <v>5485</v>
-      </c>
-      <c r="M8" s="8">
-        <f t="shared" ref="M8:M13" si="2">L8-K8</f>
-        <v>42</v>
-      </c>
-      <c r="N8" s="7">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+        <v>12200</v>
+      </c>
+      <c r="C9">
+        <v>305</v>
+      </c>
       <c r="D9" s="10" t="s">
         <v>5</v>
       </c>
@@ -826,25 +856,39 @@
       <c r="F9" s="4"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="14">
+      <c r="I9" s="16">
+        <f>305*40</f>
+        <v>12200</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" si="1"/>
+        <v>12200</v>
+      </c>
+      <c r="K9" s="5">
+        <f>70*40</f>
+        <v>2800</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="2"/>
+        <v>9400</v>
+      </c>
+      <c r="M9" s="16"/>
+      <c r="N9" s="8">
+        <f t="shared" si="3"/>
+        <v>9400</v>
+      </c>
+      <c r="O9" s="7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="7">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+        <v>2800</v>
+      </c>
+      <c r="C10">
+        <v>70</v>
+      </c>
       <c r="D10" s="10" t="s">
         <v>6</v>
       </c>
@@ -859,29 +903,36 @@
         <v>30000</v>
       </c>
       <c r="H10" s="13"/>
-      <c r="I10" s="14">
+      <c r="I10" s="13"/>
+      <c r="J10" s="14">
+        <f t="shared" si="1"/>
+        <v>40905</v>
+      </c>
+      <c r="K10" s="5">
+        <f>769.85*40</f>
+        <v>30794</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="2"/>
+        <v>10111</v>
+      </c>
+      <c r="M10" s="16"/>
+      <c r="N10" s="8">
+        <f t="shared" si="3"/>
+        <v>10111</v>
+      </c>
+      <c r="O10" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B11">
         <f t="shared" si="0"/>
-        <v>40905</v>
-      </c>
-      <c r="J10" s="5">
-        <v>24378</v>
-      </c>
-      <c r="K10" s="15">
-        <f t="shared" si="1"/>
-        <v>16527</v>
-      </c>
-      <c r="L10" s="16">
-        <v>16921</v>
-      </c>
-      <c r="M10" s="8">
-        <f t="shared" si="2"/>
-        <v>394</v>
-      </c>
-      <c r="N10" s="7">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+        <v>16000</v>
+      </c>
+      <c r="C11">
+        <v>400</v>
+      </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
@@ -895,30 +946,39 @@
         <f>203*40</f>
         <v>8120</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14">
+      <c r="H11" s="13">
+        <v>8000</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="14">
+        <f t="shared" si="1"/>
+        <v>21715</v>
+      </c>
+      <c r="K11" s="5">
+        <f>634.5*40</f>
+        <v>25380</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="2"/>
+        <v>-3665</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="N11" s="8">
+        <f t="shared" si="3"/>
+        <v>-3665</v>
+      </c>
+      <c r="O11" s="7">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B12">
         <f t="shared" si="0"/>
-        <v>13715</v>
-      </c>
-      <c r="J11" s="5">
-        <v>18944</v>
-      </c>
-      <c r="K11" s="15">
-        <f t="shared" si="1"/>
-        <v>-5229</v>
-      </c>
-      <c r="L11" s="16">
-        <v>10797</v>
-      </c>
-      <c r="M11" s="8">
-        <f t="shared" si="2"/>
-        <v>16026</v>
-      </c>
-      <c r="N11" s="7">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+        <v>2800</v>
+      </c>
+      <c r="C12">
+        <v>70</v>
+      </c>
       <c r="D12" s="10" t="s">
         <v>8</v>
       </c>
@@ -932,33 +992,33 @@
         <f>1047*40</f>
         <v>41880</v>
       </c>
-      <c r="H12" s="13">
-        <f>400*40</f>
-        <v>16000</v>
-      </c>
-      <c r="I12" s="14">
-        <f t="shared" si="0"/>
-        <v>64990</v>
-      </c>
-      <c r="J12" s="5">
-        <v>29424</v>
-      </c>
-      <c r="K12" s="15">
+      <c r="H12" s="13"/>
+      <c r="I12" s="16">
+        <f>70*40</f>
+        <v>2800</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v>35566</v>
-      </c>
-      <c r="L12" s="16">
-        <v>20322</v>
-      </c>
-      <c r="M12" s="8">
+        <v>51790</v>
+      </c>
+      <c r="K12" s="5">
+        <f>913.5*40</f>
+        <v>36540</v>
+      </c>
+      <c r="L12" s="15">
         <f t="shared" si="2"/>
-        <v>-15244</v>
-      </c>
-      <c r="N12" s="7">
+        <v>15250</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="8">
+        <f t="shared" si="3"/>
+        <v>15250</v>
+      </c>
+      <c r="O12" s="7">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D13" s="10" t="s">
         <v>9</v>
       </c>
@@ -970,29 +1030,29 @@
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="14">
-        <f t="shared" si="0"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14">
+        <f t="shared" si="1"/>
         <v>66124</v>
       </c>
-      <c r="J13" s="5">
-        <v>19350</v>
-      </c>
-      <c r="K13" s="15">
-        <f t="shared" si="1"/>
-        <v>46774</v>
-      </c>
-      <c r="L13" s="16">
-        <v>47139</v>
-      </c>
-      <c r="M13" s="8">
+      <c r="K13" s="5">
+        <f>801.7*40</f>
+        <v>32068</v>
+      </c>
+      <c r="L13" s="15">
         <f t="shared" si="2"/>
-        <v>365</v>
-      </c>
-      <c r="N13" s="7">
+        <v>34056</v>
+      </c>
+      <c r="M13" s="16"/>
+      <c r="N13" s="8">
+        <f t="shared" si="3"/>
+        <v>34056</v>
+      </c>
+      <c r="O13" s="7">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="3:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D14" s="10" t="s">
         <v>18</v>
       </c>
@@ -1006,35 +1066,39 @@
         <v>80000</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" ref="H14:N14" si="3">SUM(H7:H13)</f>
-        <v>36000</v>
+        <f t="shared" ref="H14:O14" si="4">SUM(H7:H13)</f>
+        <v>24000</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="3"/>
-        <v>225988</v>
+        <f t="shared" si="4"/>
+        <v>17800</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="3"/>
-        <v>118686</v>
+        <f t="shared" si="4"/>
+        <v>231788</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="3"/>
-        <v>107302</v>
+        <f t="shared" si="4"/>
+        <v>161810.79999999999</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="3"/>
-        <v>109043</v>
+        <f t="shared" si="4"/>
+        <v>69977.2</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" si="3"/>
-        <v>1741</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>69977.2</v>
+      </c>
+      <c r="O14" s="6">
+        <f t="shared" si="4"/>
         <v>791</v>
       </c>
     </row>
-    <row r="15" spans="3:14" ht="23" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" ht="23" x14ac:dyDescent="0.35">
       <c r="D15" s="10" t="s">
         <v>19</v>
       </c>
@@ -1044,41 +1108,45 @@
         <v>2749.7</v>
       </c>
       <c r="G15" s="12">
-        <f t="shared" ref="G15:N15" si="4">G14/40</f>
+        <f t="shared" ref="G15:O15" si="5">G14/40</f>
         <v>2000</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" si="4"/>
-        <v>900</v>
+        <f t="shared" si="5"/>
+        <v>600</v>
       </c>
       <c r="I15" s="12">
-        <f t="shared" si="4"/>
-        <v>5649.7</v>
+        <f t="shared" si="5"/>
+        <v>445</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="4"/>
-        <v>2967.15</v>
+        <f t="shared" si="5"/>
+        <v>5794.7</v>
       </c>
       <c r="K15" s="12">
-        <f t="shared" si="4"/>
-        <v>2682.55</v>
+        <f t="shared" si="5"/>
+        <v>4045.2699999999995</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="4"/>
-        <v>2726.0749999999998</v>
+        <f t="shared" si="5"/>
+        <v>1749.4299999999998</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="4"/>
-        <v>43.524999999999999</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>1749.4299999999998</v>
+      </c>
+      <c r="O15" s="12">
+        <f t="shared" si="5"/>
         <v>19.774999999999999</v>
       </c>
     </row>
-    <row r="16" spans="3:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D16" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="24" t="s">
@@ -1087,28 +1155,29 @@
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="24"/>
+      <c r="K16" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="25" t="s">
+      <c r="L16" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="L16" s="25"/>
-      <c r="M16" s="8" t="s">
+      <c r="M16" s="25"/>
+      <c r="N16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="22" t="s">
+      <c r="O16" s="22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.35">
-      <c r="J17" s="1"/>
+    <row r="17" spans="11:11" x14ac:dyDescent="0.35">
+      <c r="K17" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="D5:N5"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="D5:O5"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="L16:M16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Behind/Pimary VS Secondary.xlsx
+++ b/Behind/Pimary VS Secondary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Behind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F18C05-8900-4AF2-A96B-1274F84AB131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8660585B-A4AC-4E78-A605-643325DFC86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B13BB3DE-45F3-4A08-8C5B-C8EF34D5413B}"/>
   </bookViews>
@@ -678,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4897FB-F3E4-4933-BDE3-BEDB17D2ED6F}">
-  <dimension ref="B5:O17"/>
+  <dimension ref="C5:O17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="44.54296875" bestFit="1" customWidth="1"/>
@@ -694,7 +694,7 @@
     <col min="15" max="15" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:15" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
       <c r="D5" s="23" t="s">
         <v>21</v>
       </c>
@@ -710,7 +710,7 @@
       <c r="N5" s="23"/>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" spans="2:15" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="3:15" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C6" s="9"/>
       <c r="D6" s="17" t="s">
         <v>0</v>
@@ -749,14 +749,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B7">
-        <f>C7*40</f>
-        <v>12000</v>
-      </c>
-      <c r="C7">
-        <v>300</v>
-      </c>
+    <row r="7" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D7" s="10" t="s">
         <v>3</v>
       </c>
@@ -771,13 +764,10 @@
         <f>300*40</f>
         <v>12000</v>
       </c>
-      <c r="I7" s="16">
-        <f>70*40</f>
-        <v>2800</v>
-      </c>
+      <c r="I7" s="13"/>
       <c r="J7" s="14">
         <f>F7+G7+H7+I7</f>
-        <v>24386</v>
+        <v>21586</v>
       </c>
       <c r="K7" s="5">
         <f>394.12*40</f>
@@ -785,25 +775,18 @@
       </c>
       <c r="L7" s="15">
         <f>J7-K7</f>
-        <v>8621.2000000000007</v>
+        <v>5821.2000000000007</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="8">
         <f>L7-M7</f>
-        <v>8621.2000000000007</v>
+        <v>5821.2000000000007</v>
       </c>
       <c r="O7" s="7">
         <v>280</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <f t="shared" ref="B8:B12" si="0">C8*40</f>
-        <v>8000</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
+    <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
@@ -815,38 +798,32 @@
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13">
-        <v>4000</v>
+        <f>200*40</f>
+        <v>8000</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="14">
-        <f t="shared" ref="J8:J13" si="1">F8+G8+H8+I8</f>
-        <v>14668</v>
+        <f t="shared" ref="J8:J13" si="0">F8+G8+H8+I8</f>
+        <v>18668</v>
       </c>
       <c r="K8" s="5">
         <f>461.6*40</f>
         <v>18464</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" ref="L8:L13" si="2">J8-K8</f>
-        <v>-3796</v>
+        <f t="shared" ref="L8:L13" si="1">J8-K8</f>
+        <v>204</v>
       </c>
       <c r="M8" s="16"/>
       <c r="N8" s="8">
-        <f t="shared" ref="N8:N13" si="3">L8-M8</f>
-        <v>-3796</v>
+        <f t="shared" ref="N8:N13" si="2">L8-M8</f>
+        <v>204</v>
       </c>
       <c r="O8" s="7">
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <f t="shared" si="0"/>
-        <v>12200</v>
-      </c>
-      <c r="C9">
-        <v>305</v>
-      </c>
+    <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D9" s="10" t="s">
         <v>5</v>
       </c>
@@ -856,12 +833,12 @@
       <c r="F9" s="4"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="16">
+      <c r="I9" s="13">
         <f>305*40</f>
         <v>12200</v>
       </c>
       <c r="J9" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12200</v>
       </c>
       <c r="K9" s="5">
@@ -869,26 +846,19 @@
         <v>2800</v>
       </c>
       <c r="L9" s="15">
+        <f t="shared" si="1"/>
+        <v>9400</v>
+      </c>
+      <c r="M9" s="16"/>
+      <c r="N9" s="8">
         <f t="shared" si="2"/>
         <v>9400</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="8">
-        <f t="shared" si="3"/>
-        <v>9400</v>
-      </c>
       <c r="O9" s="7">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B10">
-        <f t="shared" si="0"/>
-        <v>2800</v>
-      </c>
-      <c r="C10">
-        <v>70</v>
-      </c>
+    <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D10" s="10" t="s">
         <v>6</v>
       </c>
@@ -903,36 +873,31 @@
         <v>30000</v>
       </c>
       <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="I10" s="13">
+        <v>2800</v>
+      </c>
       <c r="J10" s="14">
-        <f t="shared" si="1"/>
-        <v>40905</v>
+        <f t="shared" si="0"/>
+        <v>43705</v>
       </c>
       <c r="K10" s="5">
         <f>769.85*40</f>
         <v>30794</v>
       </c>
       <c r="L10" s="15">
-        <f t="shared" si="2"/>
-        <v>10111</v>
+        <f t="shared" si="1"/>
+        <v>12911</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="8">
-        <f t="shared" si="3"/>
-        <v>10111</v>
+        <f t="shared" si="2"/>
+        <v>12911</v>
       </c>
       <c r="O10" s="7">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <f t="shared" si="0"/>
-        <v>16000</v>
-      </c>
-      <c r="C11">
-        <v>400</v>
-      </c>
+    <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
@@ -947,38 +912,32 @@
         <v>8120</v>
       </c>
       <c r="H11" s="13">
-        <v>8000</v>
+        <f>400*40</f>
+        <v>16000</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="14">
-        <f t="shared" si="1"/>
-        <v>21715</v>
+        <f t="shared" si="0"/>
+        <v>29715</v>
       </c>
       <c r="K11" s="5">
         <f>634.5*40</f>
         <v>25380</v>
       </c>
       <c r="L11" s="15">
-        <f t="shared" si="2"/>
-        <v>-3665</v>
+        <f t="shared" si="1"/>
+        <v>4335</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="8">
-        <f t="shared" si="3"/>
-        <v>-3665</v>
+        <f t="shared" si="2"/>
+        <v>4335</v>
       </c>
       <c r="O11" s="7">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B12">
-        <f t="shared" si="0"/>
-        <v>2800</v>
-      </c>
-      <c r="C12">
-        <v>70</v>
-      </c>
+    <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D12" s="10" t="s">
         <v>8</v>
       </c>
@@ -993,12 +952,12 @@
         <v>41880</v>
       </c>
       <c r="H12" s="13"/>
-      <c r="I12" s="16">
+      <c r="I12" s="13">
         <f>70*40</f>
         <v>2800</v>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>51790</v>
       </c>
       <c r="K12" s="5">
@@ -1006,19 +965,19 @@
         <v>36540</v>
       </c>
       <c r="L12" s="15">
+        <f t="shared" si="1"/>
+        <v>15250</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="8">
         <f t="shared" si="2"/>
         <v>15250</v>
       </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="8">
-        <f t="shared" si="3"/>
-        <v>15250</v>
-      </c>
       <c r="O12" s="7">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:15" ht="23.5" x14ac:dyDescent="0.35">
       <c r="D13" s="10" t="s">
         <v>9</v>
       </c>
@@ -1032,7 +991,7 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>66124</v>
       </c>
       <c r="K13" s="5">
@@ -1040,19 +999,19 @@
         <v>32068</v>
       </c>
       <c r="L13" s="15">
+        <f t="shared" si="1"/>
+        <v>34056</v>
+      </c>
+      <c r="M13" s="16"/>
+      <c r="N13" s="8">
         <f t="shared" si="2"/>
         <v>34056</v>
       </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="8">
-        <f t="shared" si="3"/>
-        <v>34056</v>
-      </c>
       <c r="O13" s="7">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D14" s="10" t="s">
         <v>18</v>
       </c>
@@ -1066,39 +1025,39 @@
         <v>80000</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" ref="H14:O14" si="4">SUM(H7:H13)</f>
-        <v>24000</v>
+        <f t="shared" ref="H14:O14" si="3">SUM(H7:H13)</f>
+        <v>36000</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>17800</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="4"/>
-        <v>231788</v>
+        <f t="shared" si="3"/>
+        <v>243788</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>161810.79999999999</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="4"/>
-        <v>69977.2</v>
+        <f t="shared" si="3"/>
+        <v>81977.2</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="4"/>
-        <v>69977.2</v>
+        <f t="shared" si="3"/>
+        <v>81977.2</v>
       </c>
       <c r="O14" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>791</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="23" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:15" ht="23" x14ac:dyDescent="0.35">
       <c r="D15" s="10" t="s">
         <v>19</v>
       </c>
@@ -1108,43 +1067,43 @@
         <v>2749.7</v>
       </c>
       <c r="G15" s="12">
-        <f t="shared" ref="G15:O15" si="5">G14/40</f>
+        <f t="shared" ref="G15:O15" si="4">G14/40</f>
         <v>2000</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" si="5"/>
-        <v>600</v>
+        <f t="shared" si="4"/>
+        <v>900</v>
       </c>
       <c r="I15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>445</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="5"/>
-        <v>5794.7</v>
+        <f t="shared" si="4"/>
+        <v>6094.7</v>
       </c>
       <c r="K15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4045.2699999999995</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="5"/>
-        <v>1749.4299999999998</v>
+        <f t="shared" si="4"/>
+        <v>2049.4299999999998</v>
       </c>
       <c r="M15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" si="5"/>
-        <v>1749.4299999999998</v>
+        <f t="shared" si="4"/>
+        <v>2049.4299999999998</v>
       </c>
       <c r="O15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>19.774999999999999</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:15" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D16" s="19" t="s">
         <v>25</v>
       </c>
